--- a/utenti.xlsx
+++ b/utenti.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>mail</t>
   </si>
@@ -34,6 +34,51 @@
   </si>
   <si>
     <t>dario.rosselli@immediaspa.com</t>
+  </si>
+  <si>
+    <t>Ente</t>
+  </si>
+  <si>
+    <t>Nome</t>
+  </si>
+  <si>
+    <t>Cognome</t>
+  </si>
+  <si>
+    <t>Immedia</t>
+  </si>
+  <si>
+    <t>Donato</t>
+  </si>
+  <si>
+    <t>Gennaro</t>
+  </si>
+  <si>
+    <t>Marino</t>
+  </si>
+  <si>
+    <t>Nino</t>
+  </si>
+  <si>
+    <t>Tamara</t>
+  </si>
+  <si>
+    <t>Amata</t>
+  </si>
+  <si>
+    <t>Dario</t>
+  </si>
+  <si>
+    <t>Rosselli</t>
+  </si>
+  <si>
+    <t>Comune di Catania</t>
+  </si>
+  <si>
+    <t>Comune di Petrosino</t>
+  </si>
+  <si>
+    <t>Comune di Palermo</t>
   </si>
 </sst>
 </file>
@@ -372,51 +417,96 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="54.6640625" customWidth="1"/>
+    <col min="1" max="1" width="35.33203125" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15">
+    <row r="1" spans="1:5" ht="15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2">
         <v>123</v>
       </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3">
         <v>123456</v>
       </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4">
         <v>12345678</v>
       </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5">
         <v>123456</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
